--- a/Protokollantenliste.xlsx
+++ b/Protokollantenliste.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fhaachen-my.sharepoint.com/personal/lk3815s_ad_fh-aachen_de/Documents/FH Aachen/3. Semester/SWE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{61EC0E39-1CDD-405E-9A1E-DA222AC01C42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{61EC0E39-1CDD-405E-9A1E-DA222AC01C42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8551DB5-4B01-42C4-9032-EAEBEA282E69}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" xr2:uid="{94834BD9-14DC-4616-84CF-AC3513FA7EC0}"/>
   </bookViews>
@@ -476,7 +476,7 @@
         <v>45953</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.45">
@@ -487,7 +487,7 @@
         <v>45960</v>
       </c>
       <c r="C4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.45">
@@ -498,7 +498,7 @@
         <v>45967</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.45">
